--- a/public/templates/dmd-sales-orders.xlsx
+++ b/public/templates/dmd-sales-orders.xlsx
@@ -16,9 +16,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
-    <t>Ngày tạo</t>
-  </si>
-  <si>
     <t>Khách</t>
   </si>
   <si>
@@ -28,7 +25,13 @@
     <t>Sub-Service</t>
   </si>
   <si>
-    <t>Order ID</t>
+    <t>Client Order ID</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Lý do Discount</t>
   </si>
   <si>
     <t>Note</t>
@@ -55,6 +58,9 @@
     <t>Cao</t>
   </si>
   <si>
+    <t>Thể tích</t>
+  </si>
+  <si>
     <t>Khối lượng</t>
   </si>
   <si>
@@ -82,7 +88,7 @@
     <t>Điện thoại</t>
   </si>
   <si>
-    <t>RULE: Không đổi tên cột. Order ID là bắt buộc. Sales account được lấy tự động từ người đang đăng nhập.</t>
+    <t>RULE: Không đổi tên cột. Client Order ID là mã của khách và bắt buộc. Ngày tạo được hệ thống tự lưu. Sales account lấy từ người đang đăng nhập.</t>
   </si>
   <si>
     <t>Không nhập Supplier/Tracking/Net Cost/Base/Retail/Tax ở template Sales.</t>
@@ -192,13 +198,19 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
